--- a/inspection_forms/036_trauma_bag_checklist--inspection_forms.xlsx
+++ b/inspection_forms/036_trauma_bag_checklist--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,40 +515,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_1</t>
+          <t>trauma_bag_contents</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>Trauma Bag Contents</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2</t>
+          <t>first_responder</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>trauma_bag_contents</t>
+          <t>First Responder</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,40 +561,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_3</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>first_responder</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_4</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>trauma_bags_location</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_5</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>date_and_time</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,253 +630,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_6</t>
+          <t>missing_items</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Missing Items</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_7</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>missing_items</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_8</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>first_responder</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_9</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_10</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>missing_items</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -891,12 +661,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -919,7 +689,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>trauma_bag_contents_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -936,7 +706,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>trauma_bag_contents_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -953,559 +723,287 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>trauma_bag_contents_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>bleeding</t>
+          <t>bleeding_control</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bleeding</t>
+          <t>Bleeding control</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>trauma_bag_contents_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>broken</t>
+          <t>burn_cream</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Burn cream</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>trauma_bag_contents_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>burn</t>
+          <t>cold_pack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Cold pack</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>trauma_bag_contents_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cold</t>
+          <t>dvt_prevention_kit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>DVT prevention kit</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>trauma_bag_contents_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dvt</t>
+          <t>gauze</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DVT</t>
+          <t>Gauze</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>trauma_bag_contents_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gauze</t>
+          <t>hypothermia_prevention_kit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gauze</t>
+          <t>Hypothermia prevention kit</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>trauma_bag_contents_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hypothermia</t>
+          <t>tourniquet</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hypothermia</t>
+          <t>Tourniquet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>trauma_bag_contents_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>tourniquet</t>
+          <t>tourniquet_kit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tourniquet</t>
+          <t>Tourniquet kit</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>trauma_bag_contents_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>tourniquet</t>
+          <t>tourniquet_straight</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tourniquet</t>
+          <t>Tourniquet straight</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>trauma_bag_contents_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>tourniquet_kit</t>
+          <t>tourniquet_trap</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tourniquet_Kit</t>
+          <t>Tourniquet trap</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>trauma_bag_contents_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>tourniquet_straight</t>
+          <t>tourniquet_upper</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tourniquet_Straight</t>
+          <t>Tourniquet upper</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>first_responder_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tourniquet_trap</t>
+          <t>first_responder</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tourniquet_Trap</t>
+          <t>First Responder</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>first_responder_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>tourniquet_upper</t>
+          <t>second_responder</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tourniquet_Upper</t>
+          <t>Second Responder</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>first_responder_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>tourniquet_lower</t>
+          <t>third_responder</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tourniquet_Lower</t>
+          <t>Third Responder</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>first_responder_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>tourniquet_straight_trap</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tourniquet_Straight_Trap</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_2_choices</t>
+          <t>missing_items_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>tourniquet_upper_trap</t>
+          <t>missing_item_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tourniquet_Upper_Trap</t>
+          <t>Missing item 1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>trauma_bag_checklist_3_choices</t>
+          <t>missing_items_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>first_responder</t>
+          <t>missing_item_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>First Responder</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_3_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>first_responder</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>First Responder</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_3_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>second_responder</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Second Responder</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_3_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>third_responder</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Third Responder</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_3_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_7_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>missing_items</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Missing items</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_7_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_7_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>missing_items</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Missing items</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_7_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>item_1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_7_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>item_2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_8_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>first_responder</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>First Responder</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_8_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>first_responder</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>First Responder</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_8_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>second_responder</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Second Responder</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_8_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>third_responder</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Third Responder</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_8_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_11_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>missing_item_1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Missing item 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>trauma_bag_checklist_11_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>missing_item_2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
         <is>
           <t>Missing item 2</t>
         </is>
